--- a/grupos/2APM - Estadisticos 20232.xlsx
+++ b/grupos/2APM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="291" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="122">
   <si>
     <t>Materia</t>
   </si>
@@ -200,24 +200,24 @@
     <t>Vargas Olvera Francisco Eduardo</t>
   </si>
   <si>
+    <t>Gaspar Velazco Juan Francisco</t>
+  </si>
+  <si>
+    <t>Herrera Serrano Mayra Iliana</t>
+  </si>
+  <si>
     <t>Duran Amezcua María Angélica</t>
   </si>
   <si>
     <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
-    <t>Gaspar Velazco Juan Francisco</t>
+    <t>De Jesús Orduña Sofía del Pilar</t>
   </si>
   <si>
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
-    <t>Herrera Serrano Mayra Iliana</t>
-  </si>
-  <si>
-    <t>De Jesús Orduña Sofía del Pilar</t>
-  </si>
-  <si>
     <t>Sanchez Morales Gilberto</t>
   </si>
   <si>
@@ -236,127 +236,154 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MOLINA</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>PERALTA</t>
+  </si>
+  <si>
     <t>REYES</t>
   </si>
   <si>
+    <t>RIOS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>TETLA</t>
+  </si>
+  <si>
+    <t>AMADOR</t>
+  </si>
+  <si>
+    <t>TOLENTINO</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>NIEVES</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>TENCHIPE</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>COXCAHUA</t>
+  </si>
+  <si>
     <t>MONTIEL</t>
   </si>
   <si>
+    <t>CORREA</t>
+  </si>
+  <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
+    <t>HECTOR</t>
+  </si>
+  <si>
+    <t>JOSELYN</t>
+  </si>
+  <si>
+    <t>LEONARDO GABRIEL</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>ESTRELLA ESMERALDA</t>
+  </si>
+  <si>
+    <t>ESTRELLA RUBI</t>
+  </si>
+  <si>
+    <t>ANDREA</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>DORIAN ALEXANDER</t>
+  </si>
+  <si>
+    <t>JUAN PABLO</t>
+  </si>
+  <si>
+    <t>KEIRA</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>SALMA JANET</t>
+  </si>
+  <si>
+    <t>JESHUA</t>
+  </si>
+  <si>
+    <t>VICTOR JESUS</t>
+  </si>
+  <si>
     <t>ELIUD EDUARDO</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>TOLENTINO</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>TENCHIPE</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>ESTRELLA ESMERALDA</t>
-  </si>
-  <si>
-    <t>XOCHITL ALELI</t>
-  </si>
-  <si>
-    <t>HECTOR</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>JUAN PABLO</t>
-  </si>
-  <si>
-    <t>JOSELYN</t>
-  </si>
-  <si>
-    <t>KEIRA</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>SALMA JANET</t>
-  </si>
-  <si>
-    <t>JESHUA</t>
-  </si>
-  <si>
-    <t>VICTOR JESUS</t>
+    <t>KAORY AYELEN</t>
   </si>
   <si>
     <t>MARIEL</t>
   </si>
   <si>
     <t>VALERIA</t>
+  </si>
+  <si>
+    <t>JUAN CARLOS</t>
   </si>
 </sst>
 </file>
@@ -940,34 +967,34 @@
         <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V4">
         <v>-1</v>
@@ -1012,16 +1039,16 @@
         <v>7</v>
       </c>
       <c r="AJ4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK4">
         <v>7</v>
       </c>
       <c r="AL4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AM4">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN4">
         <v>7</v>
@@ -1065,34 +1092,34 @@
         <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V5">
         <v>-1</v>
@@ -1125,10 +1152,10 @@
         <v>-1</v>
       </c>
       <c r="AF5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH5">
         <v>10</v>
@@ -1143,13 +1170,13 @@
         <v>9</v>
       </c>
       <c r="AL5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM5">
         <v>10</v>
       </c>
       <c r="AN5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO5">
         <v>-1</v>
@@ -1190,34 +1217,34 @@
         <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V6">
         <v>-1</v>
@@ -1250,7 +1277,7 @@
         <v>-1</v>
       </c>
       <c r="AF6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG6">
         <v>8</v>
@@ -1268,10 +1295,10 @@
         <v>8</v>
       </c>
       <c r="AL6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN6">
         <v>7</v>
@@ -1315,34 +1342,34 @@
         <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V7">
         <v>-1</v>
@@ -1381,25 +1408,25 @@
         <v>7</v>
       </c>
       <c r="AH7">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI7">
         <v>7</v>
       </c>
       <c r="AJ7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM7">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AN7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO7">
         <v>-1</v>
@@ -1440,34 +1467,34 @@
         <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>-1</v>
@@ -1500,13 +1527,13 @@
         <v>-1</v>
       </c>
       <c r="AF8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG8">
         <v>7</v>
       </c>
       <c r="AH8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI8">
         <v>7</v>
@@ -1518,13 +1545,13 @@
         <v>8</v>
       </c>
       <c r="AL8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM8">
         <v>10</v>
       </c>
       <c r="AN8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO8">
         <v>-1</v>
@@ -1565,34 +1592,34 @@
         <v>10</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9">
         <v>-1</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V9">
         <v>-1</v>
@@ -1628,28 +1655,28 @@
         <v>5</v>
       </c>
       <c r="AG9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH9">
         <v>7</v>
       </c>
       <c r="AI9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO9">
         <v>-1</v>
@@ -1690,34 +1717,34 @@
         <v>10</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V10">
         <v>-1</v>
@@ -1750,13 +1777,13 @@
         <v>-1</v>
       </c>
       <c r="AF10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI10">
         <v>7</v>
@@ -1768,10 +1795,10 @@
         <v>8</v>
       </c>
       <c r="AL10">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AM10">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AN10">
         <v>6</v>
@@ -1815,34 +1842,34 @@
         <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
         <v>-1</v>
@@ -1878,10 +1905,10 @@
         <v>7</v>
       </c>
       <c r="AG11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI11">
         <v>6</v>
@@ -1896,7 +1923,7 @@
         <v>9</v>
       </c>
       <c r="AM11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN11">
         <v>6</v>
@@ -1940,34 +1967,34 @@
         <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V12">
         <v>-1</v>
@@ -2000,10 +2027,10 @@
         <v>-1</v>
       </c>
       <c r="AF12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH12">
         <v>6</v>
@@ -2018,13 +2045,13 @@
         <v>6</v>
       </c>
       <c r="AL12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AM12">
         <v>7</v>
       </c>
       <c r="AN12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO12">
         <v>-1</v>
@@ -2065,34 +2092,34 @@
         <v>10</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V13">
         <v>-1</v>
@@ -2125,7 +2152,7 @@
         <v>-1</v>
       </c>
       <c r="AF13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG13">
         <v>6</v>
@@ -2134,7 +2161,7 @@
         <v>8</v>
       </c>
       <c r="AI13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ13">
         <v>9</v>
@@ -2149,7 +2176,7 @@
         <v>10</v>
       </c>
       <c r="AN13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO13">
         <v>-1</v>
@@ -2190,34 +2217,34 @@
         <v>5</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
         <v>-1</v>
@@ -2250,16 +2277,16 @@
         <v>-1</v>
       </c>
       <c r="AF14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH14">
         <v>6</v>
       </c>
       <c r="AI14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ14">
         <v>7</v>
@@ -2274,7 +2301,7 @@
         <v>10</v>
       </c>
       <c r="AN14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO14">
         <v>-1</v>
@@ -2315,34 +2342,34 @@
         <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V15">
         <v>-1</v>
@@ -2393,7 +2420,7 @@
         <v>7</v>
       </c>
       <c r="AL15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM15">
         <v>7</v>
@@ -2440,34 +2467,34 @@
         <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V16">
         <v>-1</v>
@@ -2500,16 +2527,16 @@
         <v>-1</v>
       </c>
       <c r="AF16">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH16">
         <v>6</v>
       </c>
       <c r="AI16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ16">
         <v>8</v>
@@ -2518,7 +2545,7 @@
         <v>9</v>
       </c>
       <c r="AL16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM16">
         <v>9</v>
@@ -2565,34 +2592,34 @@
         <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
         <v>-1</v>
@@ -2634,16 +2661,16 @@
         <v>5</v>
       </c>
       <c r="AI17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK17">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM17">
         <v>5</v>
@@ -2690,34 +2717,34 @@
         <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V18">
         <v>-1</v>
@@ -2750,10 +2777,10 @@
         <v>-1</v>
       </c>
       <c r="AF18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG18">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AH18">
         <v>10</v>
@@ -2815,34 +2842,34 @@
         <v>5</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V19">
         <v>-1</v>
@@ -2881,22 +2908,22 @@
         <v>5</v>
       </c>
       <c r="AH19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ19">
         <v>5</v>
       </c>
       <c r="AK19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL19">
         <v>10</v>
       </c>
       <c r="AM19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AN19">
         <v>6</v>
@@ -2940,34 +2967,34 @@
         <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V20">
         <v>-1</v>
@@ -3000,10 +3027,10 @@
         <v>-1</v>
       </c>
       <c r="AF20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH20">
         <v>7</v>
@@ -3018,13 +3045,13 @@
         <v>8</v>
       </c>
       <c r="AL20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM20">
         <v>10</v>
       </c>
       <c r="AN20">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AO20">
         <v>-1</v>
@@ -3065,34 +3092,34 @@
         <v>5</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V21">
         <v>-1</v>
@@ -3128,7 +3155,7 @@
         <v>7</v>
       </c>
       <c r="AG21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH21">
         <v>5</v>
@@ -3143,10 +3170,10 @@
         <v>7</v>
       </c>
       <c r="AL21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AN21">
         <v>6</v>
@@ -3190,34 +3217,34 @@
         <v>10</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
         <v>-1</v>
@@ -3250,13 +3277,13 @@
         <v>-1</v>
       </c>
       <c r="AF22">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AH22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI22">
         <v>5</v>
@@ -3268,13 +3295,13 @@
         <v>7</v>
       </c>
       <c r="AL22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AN22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO22">
         <v>-1</v>
@@ -3315,34 +3342,34 @@
         <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V23">
         <v>-1</v>
@@ -3378,13 +3405,13 @@
         <v>8</v>
       </c>
       <c r="AG23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH23">
         <v>10</v>
       </c>
       <c r="AI23">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ23">
         <v>7</v>
@@ -3396,7 +3423,7 @@
         <v>9</v>
       </c>
       <c r="AM23">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AN23">
         <v>8</v>
@@ -3440,34 +3467,34 @@
         <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V24">
         <v>-1</v>
@@ -3500,31 +3527,31 @@
         <v>-1</v>
       </c>
       <c r="AF24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AG24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AM24">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AN24">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO24">
         <v>-1</v>
@@ -3565,34 +3592,34 @@
         <v>5</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V25">
         <v>-1</v>
@@ -3643,7 +3670,7 @@
         <v>5</v>
       </c>
       <c r="AL25">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AM25">
         <v>5</v>
@@ -3690,34 +3717,34 @@
         <v>10</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V26">
         <v>-1</v>
@@ -3756,7 +3783,7 @@
         <v>8</v>
       </c>
       <c r="AH26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI26">
         <v>7</v>
@@ -3765,10 +3792,10 @@
         <v>7</v>
       </c>
       <c r="AK26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL26">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AM26">
         <v>9</v>
@@ -3791,7 +3818,7 @@
         <v>8</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E27">
         <v>7</v>
@@ -3815,34 +3842,34 @@
         <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V27">
         <v>-1</v>
@@ -3875,16 +3902,16 @@
         <v>-1</v>
       </c>
       <c r="AF27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AI27">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ27">
         <v>8</v>
@@ -3893,10 +3920,10 @@
         <v>8</v>
       </c>
       <c r="AL27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AM27">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AN27">
         <v>9</v>
@@ -3940,34 +3967,34 @@
         <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V28">
         <v>-1</v>
@@ -4000,19 +4027,19 @@
         <v>-1</v>
       </c>
       <c r="AF28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG28">
         <v>7</v>
       </c>
       <c r="AH28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI28">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AJ28">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AK28">
         <v>7</v>
@@ -4021,10 +4048,10 @@
         <v>9</v>
       </c>
       <c r="AM28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO28">
         <v>-1</v>
@@ -4065,34 +4092,34 @@
         <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V29">
         <v>-1</v>
@@ -4125,22 +4152,22 @@
         <v>-1</v>
       </c>
       <c r="AF29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ29">
         <v>9</v>
       </c>
       <c r="AK29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL29">
         <v>10</v>
@@ -4190,34 +4217,34 @@
         <v>10</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V30">
         <v>-1</v>
@@ -4259,13 +4286,13 @@
         <v>10</v>
       </c>
       <c r="AI30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ30">
         <v>9</v>
       </c>
       <c r="AK30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL30">
         <v>10</v>
@@ -4315,34 +4342,34 @@
         <v>5</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V31">
         <v>-1</v>
@@ -4375,7 +4402,7 @@
         <v>-1</v>
       </c>
       <c r="AF31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG31">
         <v>5</v>
@@ -4387,13 +4414,13 @@
         <v>5</v>
       </c>
       <c r="AJ31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK31">
         <v>5</v>
       </c>
       <c r="AL31">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AM31">
         <v>5</v>
@@ -4440,34 +4467,34 @@
         <v>5</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V32">
         <v>-1</v>
@@ -4500,31 +4527,31 @@
         <v>-1</v>
       </c>
       <c r="AF32">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AG32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AI32">
         <v>7</v>
       </c>
       <c r="AJ32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK32">
         <v>7</v>
       </c>
       <c r="AL32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM32">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AN32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO32">
         <v>-1</v>
@@ -4565,34 +4592,34 @@
         <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V33">
         <v>-1</v>
@@ -4643,7 +4670,7 @@
         <v>5</v>
       </c>
       <c r="AL33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AM33">
         <v>5</v>
@@ -4690,34 +4717,34 @@
         <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V34">
         <v>-1</v>
@@ -4759,7 +4786,7 @@
         <v>5</v>
       </c>
       <c r="AI34">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AJ34">
         <v>5</v>
@@ -4768,7 +4795,7 @@
         <v>5</v>
       </c>
       <c r="AL34">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AM34">
         <v>5</v>
@@ -4976,10 +5003,10 @@
         <v>100</v>
       </c>
       <c r="M4">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N4">
-        <v>94.7</v>
+        <v>97.7</v>
       </c>
       <c r="O4">
         <v>100</v>
@@ -5006,10 +5033,10 @@
         <v>100</v>
       </c>
       <c r="W4">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X4">
-        <v>94.7</v>
+        <v>97.7</v>
       </c>
       <c r="Y4">
         <v>100</v>
@@ -5089,7 +5116,7 @@
         <v>100</v>
       </c>
       <c r="S5">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T5">
         <v>100</v>
@@ -5119,7 +5146,7 @@
         <v>100</v>
       </c>
       <c r="AC5">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AD5">
         <v>100</v>
@@ -5166,7 +5193,7 @@
         <v>100</v>
       </c>
       <c r="M6">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="N6">
         <v>100</v>
@@ -5184,7 +5211,7 @@
         <v>100</v>
       </c>
       <c r="S6">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T6">
         <v>100</v>
@@ -5196,7 +5223,7 @@
         <v>100</v>
       </c>
       <c r="W6">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="X6">
         <v>100</v>
@@ -5214,7 +5241,7 @@
         <v>100</v>
       </c>
       <c r="AC6">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AD6">
         <v>100</v>
@@ -5261,25 +5288,25 @@
         <v>100</v>
       </c>
       <c r="M7">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N7">
-        <v>94.7</v>
+        <v>97.7</v>
       </c>
       <c r="O7">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P7">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R7">
         <v>100</v>
       </c>
       <c r="S7">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T7">
         <v>100</v>
@@ -5291,25 +5318,25 @@
         <v>100</v>
       </c>
       <c r="W7">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X7">
-        <v>94.7</v>
+        <v>97.7</v>
       </c>
       <c r="Y7">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Z7">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AA7">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AB7">
         <v>100</v>
       </c>
       <c r="AC7">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AD7">
         <v>100</v>
@@ -5356,19 +5383,19 @@
         <v>100</v>
       </c>
       <c r="M8">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N8">
-        <v>94.7</v>
+        <v>97.7</v>
       </c>
       <c r="O8">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P8">
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R8">
         <v>100</v>
@@ -5386,19 +5413,19 @@
         <v>100</v>
       </c>
       <c r="W8">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X8">
-        <v>94.7</v>
+        <v>97.7</v>
       </c>
       <c r="Y8">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Z8">
         <v>100</v>
       </c>
       <c r="AA8">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AB8">
         <v>100</v>
@@ -5448,10 +5475,10 @@
         <v>100</v>
       </c>
       <c r="L9">
-        <v>94.3</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="M9">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="N9">
         <v>100</v>
@@ -5460,28 +5487,28 @@
         <v>80</v>
       </c>
       <c r="P9">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="Q9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="R9">
         <v>100</v>
       </c>
       <c r="S9">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U9">
         <v>100</v>
       </c>
       <c r="V9">
-        <v>94.3</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="W9">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="X9">
         <v>100</v>
@@ -5490,19 +5517,19 @@
         <v>80</v>
       </c>
       <c r="Z9">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="AA9">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AB9">
         <v>100</v>
       </c>
       <c r="AC9">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="AD9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AE9">
         <v>100</v>
@@ -5546,10 +5573,10 @@
         <v>100</v>
       </c>
       <c r="M10">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="N10">
-        <v>94.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O10">
         <v>100</v>
@@ -5564,7 +5591,7 @@
         <v>100</v>
       </c>
       <c r="S10">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T10">
         <v>100</v>
@@ -5576,10 +5603,10 @@
         <v>100</v>
       </c>
       <c r="W10">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="X10">
-        <v>94.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Y10">
         <v>100</v>
@@ -5594,7 +5621,7 @@
         <v>100</v>
       </c>
       <c r="AC10">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AD10">
         <v>100</v>
@@ -5638,7 +5665,7 @@
         <v>100</v>
       </c>
       <c r="L11">
-        <v>88.59999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="M11">
         <v>100</v>
@@ -5647,10 +5674,10 @@
         <v>100</v>
       </c>
       <c r="O11">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="P11">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Q11">
         <v>100</v>
@@ -5659,7 +5686,7 @@
         <v>100</v>
       </c>
       <c r="S11">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T11">
         <v>100</v>
@@ -5668,7 +5695,7 @@
         <v>100</v>
       </c>
       <c r="V11">
-        <v>88.59999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="W11">
         <v>100</v>
@@ -5677,10 +5704,10 @@
         <v>100</v>
       </c>
       <c r="Y11">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="Z11">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="AA11">
         <v>100</v>
@@ -5689,7 +5716,7 @@
         <v>100</v>
       </c>
       <c r="AC11">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AD11">
         <v>100</v>
@@ -5736,7 +5763,7 @@
         <v>100</v>
       </c>
       <c r="M12">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="N12">
         <v>100</v>
@@ -5745,10 +5772,10 @@
         <v>90</v>
       </c>
       <c r="P12">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q12">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R12">
         <v>100</v>
@@ -5757,7 +5784,7 @@
         <v>87.5</v>
       </c>
       <c r="T12">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U12">
         <v>100</v>
@@ -5766,7 +5793,7 @@
         <v>100</v>
       </c>
       <c r="W12">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="X12">
         <v>100</v>
@@ -5775,10 +5802,10 @@
         <v>90</v>
       </c>
       <c r="Z12">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AA12">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AB12">
         <v>100</v>
@@ -5787,7 +5814,7 @@
         <v>87.5</v>
       </c>
       <c r="AD12">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AE12">
         <v>100</v>
@@ -5831,7 +5858,7 @@
         <v>100</v>
       </c>
       <c r="M13">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N13">
         <v>100</v>
@@ -5861,7 +5888,7 @@
         <v>100</v>
       </c>
       <c r="W13">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X13">
         <v>100</v>
@@ -5923,19 +5950,19 @@
         <v>100</v>
       </c>
       <c r="L14">
-        <v>94.3</v>
+        <v>95.7</v>
       </c>
       <c r="M14">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="N14">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="O14">
         <v>90</v>
       </c>
       <c r="P14">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Q14">
         <v>100</v>
@@ -5944,28 +5971,28 @@
         <v>100</v>
       </c>
       <c r="S14">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T14">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="U14">
         <v>100</v>
       </c>
       <c r="V14">
-        <v>94.3</v>
+        <v>95.7</v>
       </c>
       <c r="W14">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="X14">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Y14">
         <v>90</v>
       </c>
       <c r="Z14">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="AA14">
         <v>100</v>
@@ -5974,10 +6001,10 @@
         <v>100</v>
       </c>
       <c r="AC14">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AD14">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AE14">
         <v>100</v>
@@ -6021,16 +6048,16 @@
         <v>94.3</v>
       </c>
       <c r="M15">
-        <v>75</v>
+        <v>81.8</v>
       </c>
       <c r="N15">
-        <v>94.7</v>
+        <v>97.7</v>
       </c>
       <c r="O15">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="P15">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q15">
         <v>100</v>
@@ -6039,10 +6066,10 @@
         <v>100</v>
       </c>
       <c r="S15">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="T15">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U15">
         <v>100</v>
@@ -6051,16 +6078,16 @@
         <v>94.3</v>
       </c>
       <c r="W15">
-        <v>75</v>
+        <v>81.8</v>
       </c>
       <c r="X15">
-        <v>94.7</v>
+        <v>97.7</v>
       </c>
       <c r="Y15">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="Z15">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AA15">
         <v>100</v>
@@ -6069,10 +6096,10 @@
         <v>100</v>
       </c>
       <c r="AC15">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="AD15">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AE15">
         <v>100</v>
@@ -6116,10 +6143,10 @@
         <v>100</v>
       </c>
       <c r="M16">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="N16">
-        <v>94.7</v>
+        <v>97.7</v>
       </c>
       <c r="O16">
         <v>90</v>
@@ -6134,7 +6161,7 @@
         <v>100</v>
       </c>
       <c r="S16">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T16">
         <v>100</v>
@@ -6146,10 +6173,10 @@
         <v>100</v>
       </c>
       <c r="W16">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="X16">
-        <v>94.7</v>
+        <v>97.7</v>
       </c>
       <c r="Y16">
         <v>90</v>
@@ -6164,7 +6191,7 @@
         <v>100</v>
       </c>
       <c r="AC16">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AD16">
         <v>100</v>
@@ -6208,28 +6235,28 @@
         <v>100</v>
       </c>
       <c r="L17">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="M17">
-        <v>75</v>
+        <v>77.3</v>
       </c>
       <c r="N17">
-        <v>94.7</v>
+        <v>97.7</v>
       </c>
       <c r="O17">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P17">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="Q17">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="R17">
         <v>100</v>
       </c>
       <c r="S17">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T17">
         <v>95</v>
@@ -6238,28 +6265,28 @@
         <v>100</v>
       </c>
       <c r="V17">
-        <v>100</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="W17">
-        <v>75</v>
+        <v>77.3</v>
       </c>
       <c r="X17">
-        <v>94.7</v>
+        <v>97.7</v>
       </c>
       <c r="Y17">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Z17">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="AA17">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="AB17">
         <v>100</v>
       </c>
       <c r="AC17">
-        <v>93.8</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AD17">
         <v>95</v>
@@ -6306,10 +6333,10 @@
         <v>100</v>
       </c>
       <c r="M18">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N18">
-        <v>94.7</v>
+        <v>97.7</v>
       </c>
       <c r="O18">
         <v>100</v>
@@ -6324,7 +6351,7 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T18">
         <v>100</v>
@@ -6336,10 +6363,10 @@
         <v>100</v>
       </c>
       <c r="W18">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X18">
-        <v>94.7</v>
+        <v>97.7</v>
       </c>
       <c r="Y18">
         <v>100</v>
@@ -6354,7 +6381,7 @@
         <v>100</v>
       </c>
       <c r="AC18">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AD18">
         <v>100</v>
@@ -6398,22 +6425,22 @@
         <v>100</v>
       </c>
       <c r="L19">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="M19">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="N19">
-        <v>94.7</v>
+        <v>97.7</v>
       </c>
       <c r="O19">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="P19">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="Q19">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="R19">
         <v>100</v>
@@ -6422,28 +6449,28 @@
         <v>93.8</v>
       </c>
       <c r="T19">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="U19">
         <v>100</v>
       </c>
       <c r="V19">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="W19">
-        <v>83.3</v>
+        <v>81.8</v>
       </c>
       <c r="X19">
-        <v>94.7</v>
+        <v>97.7</v>
       </c>
       <c r="Y19">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="Z19">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="AA19">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="AB19">
         <v>100</v>
@@ -6452,7 +6479,7 @@
         <v>93.8</v>
       </c>
       <c r="AD19">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AE19">
         <v>100</v>
@@ -6514,7 +6541,7 @@
         <v>100</v>
       </c>
       <c r="S20">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T20">
         <v>100</v>
@@ -6544,7 +6571,7 @@
         <v>100</v>
       </c>
       <c r="AC20">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AD20">
         <v>100</v>
@@ -6591,10 +6618,10 @@
         <v>100</v>
       </c>
       <c r="M21">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="N21">
-        <v>94.7</v>
+        <v>97.7</v>
       </c>
       <c r="O21">
         <v>100</v>
@@ -6621,10 +6648,10 @@
         <v>100</v>
       </c>
       <c r="W21">
-        <v>91.7</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="X21">
-        <v>94.7</v>
+        <v>97.7</v>
       </c>
       <c r="Y21">
         <v>100</v>
@@ -6686,16 +6713,16 @@
         <v>100</v>
       </c>
       <c r="M22">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N22">
-        <v>94.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O22">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P22">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q22">
         <v>96</v>
@@ -6704,10 +6731,10 @@
         <v>100</v>
       </c>
       <c r="S22">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T22">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="U22">
         <v>100</v>
@@ -6716,16 +6743,16 @@
         <v>100</v>
       </c>
       <c r="W22">
-        <v>83.3</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X22">
-        <v>94.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Y22">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Z22">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AA22">
         <v>96</v>
@@ -6734,10 +6761,10 @@
         <v>100</v>
       </c>
       <c r="AC22">
-        <v>87.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AD22">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="AE22">
         <v>100</v>
@@ -6778,28 +6805,28 @@
         <v>100</v>
       </c>
       <c r="L23">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M23">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="N23">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="O23">
         <v>90</v>
       </c>
       <c r="P23">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="Q23">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="R23">
         <v>100</v>
       </c>
       <c r="S23">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="T23">
         <v>100</v>
@@ -6808,28 +6835,28 @@
         <v>100</v>
       </c>
       <c r="V23">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="W23">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="X23">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="Y23">
         <v>90</v>
       </c>
       <c r="Z23">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="AA23">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AB23">
         <v>100</v>
       </c>
       <c r="AC23">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="AD23">
         <v>100</v>
@@ -6873,28 +6900,28 @@
         <v>100</v>
       </c>
       <c r="L24">
-        <v>88.59999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="M24">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N24">
-        <v>94.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O24">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P24">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q24">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R24">
         <v>100</v>
       </c>
       <c r="S24">
-        <v>75</v>
+        <v>81.3</v>
       </c>
       <c r="T24">
         <v>100</v>
@@ -6903,28 +6930,28 @@
         <v>100</v>
       </c>
       <c r="V24">
-        <v>88.59999999999999</v>
+        <v>94.3</v>
       </c>
       <c r="W24">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X24">
-        <v>94.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Y24">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="Z24">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AA24">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AB24">
         <v>100</v>
       </c>
       <c r="AC24">
-        <v>75</v>
+        <v>81.3</v>
       </c>
       <c r="AD24">
         <v>100</v>
@@ -6968,28 +6995,28 @@
         <v>100</v>
       </c>
       <c r="L25">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="M25">
-        <v>75</v>
+        <v>68.2</v>
       </c>
       <c r="N25">
-        <v>89.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="O25">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P25">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="Q25">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="R25">
         <v>100</v>
       </c>
       <c r="S25">
-        <v>81.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="T25">
         <v>85</v>
@@ -6998,28 +7025,28 @@
         <v>100</v>
       </c>
       <c r="V25">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="W25">
-        <v>75</v>
+        <v>68.2</v>
       </c>
       <c r="X25">
-        <v>89.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="Y25">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Z25">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="AA25">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="AB25">
         <v>100</v>
       </c>
       <c r="AC25">
-        <v>81.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="AD25">
         <v>85</v>
@@ -7066,10 +7093,10 @@
         <v>100</v>
       </c>
       <c r="M26">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N26">
-        <v>94.7</v>
+        <v>97.7</v>
       </c>
       <c r="O26">
         <v>100</v>
@@ -7084,7 +7111,7 @@
         <v>100</v>
       </c>
       <c r="S26">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T26">
         <v>100</v>
@@ -7096,10 +7123,10 @@
         <v>100</v>
       </c>
       <c r="W26">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X26">
-        <v>94.7</v>
+        <v>97.7</v>
       </c>
       <c r="Y26">
         <v>100</v>
@@ -7114,7 +7141,7 @@
         <v>100</v>
       </c>
       <c r="AC26">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AD26">
         <v>100</v>
@@ -7134,7 +7161,7 @@
         <v>91.7</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E27">
         <v>100</v>
@@ -7161,16 +7188,16 @@
         <v>100</v>
       </c>
       <c r="M27">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="N27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O27">
         <v>100</v>
       </c>
       <c r="P27">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="Q27">
         <v>100</v>
@@ -7191,16 +7218,16 @@
         <v>100</v>
       </c>
       <c r="W27">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="X27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Y27">
         <v>100</v>
       </c>
       <c r="Z27">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="AA27">
         <v>100</v>
@@ -7253,10 +7280,10 @@
         <v>100</v>
       </c>
       <c r="L28">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="M28">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="N28">
         <v>100</v>
@@ -7277,16 +7304,16 @@
         <v>87.5</v>
       </c>
       <c r="T28">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="U28">
         <v>100</v>
       </c>
       <c r="V28">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="W28">
-        <v>91.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="X28">
         <v>100</v>
@@ -7307,7 +7334,7 @@
         <v>87.5</v>
       </c>
       <c r="AD28">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="AE28">
         <v>100</v>
@@ -7351,10 +7378,10 @@
         <v>100</v>
       </c>
       <c r="M29">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="N29">
-        <v>94.7</v>
+        <v>97.7</v>
       </c>
       <c r="O29">
         <v>100</v>
@@ -7369,7 +7396,7 @@
         <v>100</v>
       </c>
       <c r="S29">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="T29">
         <v>100</v>
@@ -7381,10 +7408,10 @@
         <v>100</v>
       </c>
       <c r="W29">
-        <v>91.7</v>
+        <v>95.5</v>
       </c>
       <c r="X29">
-        <v>94.7</v>
+        <v>97.7</v>
       </c>
       <c r="Y29">
         <v>100</v>
@@ -7399,7 +7426,7 @@
         <v>100</v>
       </c>
       <c r="AC29">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AD29">
         <v>100</v>
@@ -7446,7 +7473,7 @@
         <v>100</v>
       </c>
       <c r="M30">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="N30">
         <v>100</v>
@@ -7476,7 +7503,7 @@
         <v>100</v>
       </c>
       <c r="W30">
-        <v>100</v>
+        <v>95.5</v>
       </c>
       <c r="X30">
         <v>100</v>
@@ -7538,61 +7565,61 @@
         <v>100</v>
       </c>
       <c r="L31">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M31">
-        <v>75</v>
+        <v>72.7</v>
       </c>
       <c r="N31">
-        <v>89.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O31">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="P31">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q31">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R31">
         <v>100</v>
       </c>
       <c r="S31">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="T31">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="U31">
         <v>100</v>
       </c>
       <c r="V31">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="W31">
-        <v>75</v>
+        <v>72.7</v>
       </c>
       <c r="X31">
-        <v>89.5</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="Y31">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="Z31">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AA31">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="AB31">
         <v>100</v>
       </c>
       <c r="AC31">
-        <v>93.8</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AD31">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="AE31">
         <v>100</v>
@@ -7633,13 +7660,13 @@
         <v>100</v>
       </c>
       <c r="L32">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="M32">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="N32">
-        <v>94.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O32">
         <v>100</v>
@@ -7654,22 +7681,22 @@
         <v>100</v>
       </c>
       <c r="S32">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="T32">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="U32">
         <v>100</v>
       </c>
       <c r="V32">
-        <v>94.3</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="W32">
-        <v>83.3</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="X32">
-        <v>94.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Y32">
         <v>100</v>
@@ -7684,10 +7711,10 @@
         <v>100</v>
       </c>
       <c r="AC32">
-        <v>75</v>
+        <v>87.5</v>
       </c>
       <c r="AD32">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="AE32">
         <v>100</v>
@@ -7728,61 +7755,61 @@
         <v>100</v>
       </c>
       <c r="L33">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="M33">
-        <v>66.7</v>
+        <v>63.6</v>
       </c>
       <c r="N33">
-        <v>94.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O33">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="P33">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q33">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="R33">
         <v>100</v>
       </c>
       <c r="S33">
-        <v>68.8</v>
+        <v>81.3</v>
       </c>
       <c r="T33">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="U33">
         <v>100</v>
       </c>
       <c r="V33">
-        <v>100</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="W33">
-        <v>66.7</v>
+        <v>63.6</v>
       </c>
       <c r="X33">
-        <v>94.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Y33">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="Z33">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="AA33">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="AB33">
         <v>100</v>
       </c>
       <c r="AC33">
-        <v>68.8</v>
+        <v>81.3</v>
       </c>
       <c r="AD33">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AE33">
         <v>100</v>
@@ -7823,28 +7850,28 @@
         <v>100</v>
       </c>
       <c r="L34">
-        <v>94.3</v>
+        <v>95.7</v>
       </c>
       <c r="M34">
-        <v>83.3</v>
+        <v>77.3</v>
       </c>
       <c r="N34">
-        <v>94.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="O34">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="P34">
         <v>96</v>
       </c>
       <c r="Q34">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="R34">
         <v>100</v>
       </c>
       <c r="S34">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="T34">
         <v>100</v>
@@ -7853,28 +7880,28 @@
         <v>100</v>
       </c>
       <c r="V34">
-        <v>94.3</v>
+        <v>95.7</v>
       </c>
       <c r="W34">
-        <v>83.3</v>
+        <v>77.3</v>
       </c>
       <c r="X34">
-        <v>94.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="Y34">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Z34">
         <v>96</v>
       </c>
       <c r="AA34">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="AB34">
         <v>100</v>
       </c>
       <c r="AC34">
-        <v>87.5</v>
+        <v>93.8</v>
       </c>
       <c r="AD34">
         <v>100</v>
@@ -7966,7 +7993,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>60</v>
@@ -7975,30 +8002,30 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F3" s="2">
-        <v>54.8</v>
+        <v>64.5</v>
       </c>
       <c r="G3" s="2">
-        <v>41.9</v>
+        <v>35.5</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="2">
-        <v>3.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
@@ -8007,19 +8034,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>64.5</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>35.5</v>
+        <v>22.6</v>
       </c>
       <c r="H4">
-        <v>6.4</v>
+        <v>6.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -8030,7 +8057,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
@@ -8039,19 +8066,19 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F5" s="2">
-        <v>64.5</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>35.5</v>
+        <v>22.6</v>
       </c>
       <c r="H5">
-        <v>6.5</v>
+        <v>7.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -8062,7 +8089,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>63</v>
@@ -8071,19 +8098,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F6" s="2">
-        <v>77.40000000000001</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>22.6</v>
+        <v>19.4</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -8094,7 +8121,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>64</v>
@@ -8103,19 +8130,19 @@
         <v>31</v>
       </c>
       <c r="D7">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2">
-        <v>80.59999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="G7" s="2">
-        <v>19.4</v>
+        <v>16.1</v>
       </c>
       <c r="H7">
-        <v>6.7</v>
+        <v>7.2</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -8126,7 +8153,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
         <v>65</v>
@@ -8147,7 +8174,7 @@
         <v>16.1</v>
       </c>
       <c r="H8">
-        <v>7.1</v>
+        <v>8.1</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -8158,28 +8185,28 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C9">
         <v>31</v>
       </c>
       <c r="D9">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F9" s="2">
-        <v>87.09999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="G9" s="2">
-        <v>12.9</v>
+        <v>16.1</v>
       </c>
       <c r="H9">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -8190,10 +8217,10 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C10">
         <v>31</v>
@@ -8211,7 +8238,7 @@
         <v>12.9</v>
       </c>
       <c r="H10">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -8231,19 +8258,19 @@
         <v>31</v>
       </c>
       <c r="D11">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="G11" s="2">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H11">
-        <v>7.6</v>
+        <v>8.5</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -8259,7 +8286,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8286,26 +8313,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>23330051920354</v>
-      </c>
-      <c r="B2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>60</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -8313,7 +8320,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:G25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8345,19 +8352,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920155</v>
+        <v>23330051920160</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
         <v>60</v>
@@ -8368,16 +8375,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920155</v>
+        <v>23330051920160</v>
       </c>
       <c r="B3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
         <v>14</v>
@@ -8391,22 +8398,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920325</v>
+        <v>23330051920161</v>
       </c>
       <c r="B4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -8414,16 +8421,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920325</v>
+        <v>23330051920161</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
         <v>14</v>
@@ -8437,19 +8444,19 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920160</v>
+        <v>23330051920166</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D6" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
         <v>61</v>
@@ -8460,16 +8467,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920160</v>
+        <v>23330051920166</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="D7" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
         <v>14</v>
@@ -8483,22 +8490,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920354</v>
+        <v>23330051920152</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G8">
         <v>-1</v>
@@ -8506,16 +8513,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920354</v>
+        <v>23330051920153</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="D9" t="s">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="E9" t="s">
         <v>14</v>
@@ -8529,16 +8536,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920152</v>
+        <v>23330051920155</v>
       </c>
       <c r="B10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D10" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="E10" t="s">
         <v>14</v>
@@ -8552,16 +8559,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920153</v>
+        <v>23330051920154</v>
       </c>
       <c r="B11" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D11" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E11" t="s">
         <v>14</v>
@@ -8575,16 +8582,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920157</v>
+        <v>23330051920250</v>
       </c>
       <c r="B12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D12" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="E12" t="s">
         <v>14</v>
@@ -8598,16 +8605,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920159</v>
+        <v>23330051920157</v>
       </c>
       <c r="B13" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="D13" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E13" t="s">
         <v>14</v>
@@ -8621,16 +8628,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920161</v>
+        <v>23330051920158</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D14" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="E14" t="s">
         <v>14</v>
@@ -8644,16 +8651,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920163</v>
+        <v>23330051920159</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C15" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="D15" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="E15" t="s">
         <v>14</v>
@@ -8667,16 +8674,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920297</v>
+        <v>23330051920163</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C16" t="s">
         <v>95</v>
       </c>
       <c r="D16" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E16" t="s">
         <v>14</v>
@@ -8690,16 +8697,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920167</v>
+        <v>23330051920297</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="E17" t="s">
         <v>14</v>
@@ -8713,16 +8720,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920310</v>
+        <v>23330051920167</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C18" t="s">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="E18" t="s">
         <v>14</v>
@@ -8736,16 +8743,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920169</v>
+        <v>23330051920310</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="C19" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="D19" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E19" t="s">
         <v>14</v>
@@ -8759,16 +8766,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920173</v>
+        <v>23330051920169</v>
       </c>
       <c r="B20" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C20" t="s">
         <v>97</v>
       </c>
       <c r="D20" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E20" t="s">
         <v>14</v>
@@ -8782,16 +8789,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920172</v>
+        <v>23330051920354</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D21" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E21" t="s">
         <v>14</v>
@@ -8800,6 +8807,98 @@
         <v>59</v>
       </c>
       <c r="G21">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>23330051920170</v>
+      </c>
+      <c r="B22" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" t="s">
+        <v>99</v>
+      </c>
+      <c r="D22" t="s">
+        <v>118</v>
+      </c>
+      <c r="E22" t="s">
+        <v>14</v>
+      </c>
+      <c r="F22" t="s">
+        <v>59</v>
+      </c>
+      <c r="G22">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>23330051920173</v>
+      </c>
+      <c r="B23" t="s">
+        <v>85</v>
+      </c>
+      <c r="C23" t="s">
+        <v>100</v>
+      </c>
+      <c r="D23" t="s">
+        <v>119</v>
+      </c>
+      <c r="E23" t="s">
+        <v>14</v>
+      </c>
+      <c r="F23" t="s">
+        <v>59</v>
+      </c>
+      <c r="G23">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>23330051920172</v>
+      </c>
+      <c r="B24" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D24" t="s">
+        <v>120</v>
+      </c>
+      <c r="E24" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" t="s">
+        <v>59</v>
+      </c>
+      <c r="G24">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>23330051920174</v>
+      </c>
+      <c r="B25" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" t="s">
+        <v>87</v>
+      </c>
+      <c r="D25" t="s">
+        <v>121</v>
+      </c>
+      <c r="E25" t="s">
+        <v>14</v>
+      </c>
+      <c r="F25" t="s">
+        <v>59</v>
+      </c>
+      <c r="G25">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2APM - Estadisticos 20232.xlsx
+++ b/grupos/2APM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="135">
   <si>
     <t>Materia</t>
   </si>
@@ -203,27 +203,27 @@
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
+    <t>Duran Amezcua María Angélica</t>
+  </si>
+  <si>
+    <t>Sanchez Morales Gilberto</t>
+  </si>
+  <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
+    <t>De Jesús Orduña Sofía del Pilar</t>
+  </si>
+  <si>
     <t>Herrera Serrano Mayra Iliana</t>
   </si>
   <si>
-    <t>Duran Amezcua María Angélica</t>
-  </si>
-  <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
-    <t>De Jesús Orduña Sofía del Pilar</t>
+    <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
-    <t>Sanchez Morales Gilberto</t>
-  </si>
-  <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -236,33 +236,48 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LARRACILLA</t>
+  </si>
+  <si>
+    <t>VIVANCO</t>
+  </si>
+  <si>
+    <t>ABREGO</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>BONILLA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
     <t>HERRERA</t>
   </si>
   <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MELO</t>
+  </si>
+  <si>
     <t>MOLINA</t>
   </si>
   <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>ORTIZ</t>
   </si>
   <si>
@@ -284,33 +299,39 @@
     <t>TEXCAHUA</t>
   </si>
   <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>TOLENTINO</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>NIEVES</t>
+  </si>
+  <si>
+    <t>ANDRADE</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>TETLA</t>
   </si>
   <si>
     <t>AMADOR</t>
   </si>
   <si>
-    <t>TOLENTINO</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
     <t>TENCHIPE</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>COXCAHUA</t>
   </si>
   <si>
@@ -323,43 +344,61 @@
     <t>DE LA CRUZ</t>
   </si>
   <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>MONICA</t>
+  </si>
+  <si>
+    <t>LUIS AARON</t>
+  </si>
+  <si>
+    <t>SULU ALAN</t>
+  </si>
+  <si>
+    <t>JOSE ANTONIO</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>ESTRELLA ESMERALDA</t>
+  </si>
+  <si>
+    <t>ESTRELLA RUBI</t>
+  </si>
+  <si>
+    <t>XOCHITL ALELI</t>
+  </si>
+  <si>
+    <t>ANDREA</t>
+  </si>
+  <si>
+    <t>JAIR</t>
+  </si>
+  <si>
+    <t>DORIAN ALEXANDER</t>
+  </si>
+  <si>
+    <t>JUAN PABLO</t>
+  </si>
+  <si>
     <t>HECTOR</t>
   </si>
   <si>
     <t>JOSELYN</t>
   </si>
   <si>
+    <t>KEIRA</t>
+  </si>
+  <si>
+    <t>URIEL</t>
+  </si>
+  <si>
+    <t>KENYA MARIANA</t>
+  </si>
+  <si>
     <t>LEONARDO GABRIEL</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>ESTRELLA ESMERALDA</t>
-  </si>
-  <si>
-    <t>ESTRELLA RUBI</t>
-  </si>
-  <si>
-    <t>ANDREA</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>DORIAN ALEXANDER</t>
-  </si>
-  <si>
-    <t>JUAN PABLO</t>
-  </si>
-  <si>
-    <t>KEIRA</t>
-  </si>
-  <si>
-    <t>URIEL</t>
   </si>
   <si>
     <t>SALMA JANET</t>
@@ -997,43 +1036,43 @@
         <v>10</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AD4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF4">
         <v>7</v>
       </c>
       <c r="AG4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI4">
         <v>7</v>
@@ -1045,13 +1084,13 @@
         <v>7</v>
       </c>
       <c r="AL4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM4">
         <v>8</v>
       </c>
       <c r="AN4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO4">
         <v>-1</v>
@@ -1122,34 +1161,34 @@
         <v>10</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AD5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AE5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF5">
         <v>10</v>
@@ -1247,34 +1286,34 @@
         <v>10</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AD6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AE6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF6">
         <v>8</v>
@@ -1286,13 +1325,13 @@
         <v>9</v>
       </c>
       <c r="AI6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ6">
         <v>8</v>
       </c>
       <c r="AK6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL6">
         <v>9</v>
@@ -1372,34 +1411,34 @@
         <v>10</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AD7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF7">
         <v>6</v>
@@ -1411,10 +1450,10 @@
         <v>7</v>
       </c>
       <c r="AI7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK7">
         <v>7</v>
@@ -1426,7 +1465,7 @@
         <v>9</v>
       </c>
       <c r="AN7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO7">
         <v>-1</v>
@@ -1497,37 +1536,37 @@
         <v>10</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AD8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG8">
         <v>7</v>
@@ -1539,7 +1578,7 @@
         <v>7</v>
       </c>
       <c r="AJ8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK8">
         <v>8</v>
@@ -1548,10 +1587,10 @@
         <v>8</v>
       </c>
       <c r="AM8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO8">
         <v>-1</v>
@@ -1598,7 +1637,7 @@
         <v>7</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
         <v>5</v>
@@ -1622,46 +1661,46 @@
         <v>10</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AD9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AE9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ9">
         <v>7</v>
@@ -1676,7 +1715,7 @@
         <v>9</v>
       </c>
       <c r="AN9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO9">
         <v>-1</v>
@@ -1747,55 +1786,55 @@
         <v>10</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AD10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AG10">
         <v>8</v>
       </c>
       <c r="AH10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AI10">
         <v>7</v>
       </c>
       <c r="AJ10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM10">
         <v>8</v>
@@ -1872,34 +1911,34 @@
         <v>10</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AD11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF11">
         <v>7</v>
@@ -1914,7 +1953,7 @@
         <v>6</v>
       </c>
       <c r="AJ11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK11">
         <v>7</v>
@@ -1997,37 +2036,37 @@
         <v>10</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AD12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG12">
         <v>6</v>
@@ -2036,7 +2075,7 @@
         <v>6</v>
       </c>
       <c r="AI12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ12">
         <v>7</v>
@@ -2122,40 +2161,40 @@
         <v>10</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AD13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AE13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF13">
         <v>9</v>
       </c>
       <c r="AG13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH13">
         <v>8</v>
@@ -2247,40 +2286,40 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AD14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AE14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH14">
         <v>6</v>
@@ -2289,16 +2328,16 @@
         <v>7</v>
       </c>
       <c r="AJ14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL14">
         <v>9</v>
       </c>
       <c r="AM14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AN14">
         <v>8</v>
@@ -2372,37 +2411,37 @@
         <v>10</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AD15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG15">
         <v>5</v>
@@ -2411,7 +2450,7 @@
         <v>6</v>
       </c>
       <c r="AI15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AJ15">
         <v>7</v>
@@ -2423,7 +2462,7 @@
         <v>8</v>
       </c>
       <c r="AM15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN15">
         <v>6</v>
@@ -2497,52 +2536,52 @@
         <v>10</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AD16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AE16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF16">
         <v>8</v>
       </c>
       <c r="AG16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH16">
         <v>6</v>
       </c>
       <c r="AI16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AJ16">
         <v>8</v>
       </c>
       <c r="AK16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL16">
         <v>9</v>
@@ -2622,58 +2661,58 @@
         <v>10</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AA17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AD17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG17">
         <v>5</v>
       </c>
       <c r="AH17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ17">
         <v>7</v>
       </c>
       <c r="AK17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL17">
         <v>8</v>
       </c>
       <c r="AM17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AN17">
         <v>5</v>
@@ -2747,34 +2786,34 @@
         <v>10</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AD18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF18">
         <v>8</v>
@@ -2801,7 +2840,7 @@
         <v>10</v>
       </c>
       <c r="AN18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AO18">
         <v>-1</v>
@@ -2872,58 +2911,58 @@
         <v>10</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Z19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AD19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF19">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG19">
         <v>5</v>
       </c>
       <c r="AH19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ19">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK19">
         <v>6</v>
       </c>
       <c r="AL19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AM19">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN19">
         <v>6</v>
@@ -2997,40 +3036,40 @@
         <v>10</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AD20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AE20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF20">
         <v>9</v>
       </c>
       <c r="AG20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AH20">
         <v>7</v>
@@ -3051,7 +3090,7 @@
         <v>10</v>
       </c>
       <c r="AN20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO20">
         <v>-1</v>
@@ -3122,49 +3161,49 @@
         <v>10</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AD21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF21">
         <v>7</v>
       </c>
       <c r="AG21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AH21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AJ21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK21">
         <v>7</v>
@@ -3247,37 +3286,37 @@
         <v>10</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AB22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AD22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG22">
         <v>7</v>
@@ -3286,22 +3325,22 @@
         <v>8</v>
       </c>
       <c r="AI22">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AJ22">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK22">
         <v>7</v>
       </c>
       <c r="AL22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM22">
         <v>8</v>
       </c>
       <c r="AN22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO22">
         <v>-1</v>
@@ -3372,34 +3411,34 @@
         <v>10</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AC23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AD23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF23">
         <v>8</v>
@@ -3420,13 +3459,13 @@
         <v>7</v>
       </c>
       <c r="AL23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM23">
         <v>8</v>
       </c>
       <c r="AN23">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO23">
         <v>-1</v>
@@ -3497,52 +3536,52 @@
         <v>10</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AD24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AE24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF24">
         <v>8</v>
       </c>
       <c r="AG24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ24">
         <v>7</v>
       </c>
       <c r="AK24">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AL24">
         <v>9</v>
@@ -3551,7 +3590,7 @@
         <v>9</v>
       </c>
       <c r="AN24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO24">
         <v>-1</v>
@@ -3622,34 +3661,34 @@
         <v>10</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="X25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AD25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF25">
         <v>5</v>
@@ -3661,19 +3700,19 @@
         <v>5</v>
       </c>
       <c r="AI25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ25">
         <v>5</v>
       </c>
       <c r="AK25">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL25">
         <v>8</v>
       </c>
       <c r="AM25">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AN25">
         <v>5</v>
@@ -3747,34 +3786,34 @@
         <v>10</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Z26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AD26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AE26">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF26">
         <v>8</v>
@@ -3786,7 +3825,7 @@
         <v>8</v>
       </c>
       <c r="AI26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ26">
         <v>7</v>
@@ -3795,13 +3834,13 @@
         <v>8</v>
       </c>
       <c r="AL26">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM26">
         <v>9</v>
       </c>
       <c r="AN26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO26">
         <v>-1</v>
@@ -3872,34 +3911,34 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AB27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AD27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AE27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF27">
         <v>8</v>
@@ -3920,7 +3959,7 @@
         <v>8</v>
       </c>
       <c r="AL27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM27">
         <v>9</v>
@@ -3997,34 +4036,34 @@
         <v>10</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AD28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF28">
         <v>7</v>
@@ -4051,7 +4090,7 @@
         <v>7</v>
       </c>
       <c r="AN28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO28">
         <v>-1</v>
@@ -4122,34 +4161,34 @@
         <v>10</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AD29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AE29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF29">
         <v>8</v>
@@ -4161,13 +4200,13 @@
         <v>8</v>
       </c>
       <c r="AI29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AJ29">
         <v>9</v>
       </c>
       <c r="AK29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL29">
         <v>10</v>
@@ -4247,34 +4286,34 @@
         <v>10</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Y30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Z30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AA30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AD30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AE30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF30">
         <v>9</v>
@@ -4372,37 +4411,37 @@
         <v>10</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AA31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AC31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AD31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AE31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF31">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG31">
         <v>5</v>
@@ -4411,19 +4450,19 @@
         <v>5</v>
       </c>
       <c r="AI31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ31">
         <v>6</v>
       </c>
       <c r="AK31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN31">
         <v>5</v>
@@ -4497,43 +4536,43 @@
         <v>10</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AA32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AB32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AD32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI32">
         <v>7</v>
@@ -4542,16 +4581,16 @@
         <v>7</v>
       </c>
       <c r="AK32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM32">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AN32">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO32">
         <v>-1</v>
@@ -4622,61 +4661,61 @@
         <v>10</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="X33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Y33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Z33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AA33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AB33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AD33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AE33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG33">
         <v>5</v>
       </c>
       <c r="AH33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ33">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AK33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AM33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN33">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO33">
         <v>-1</v>
@@ -4747,34 +4786,34 @@
         <v>10</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="X34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Z34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AA34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AB34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AC34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AD34">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="AE34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AF34">
         <v>5</v>
@@ -4786,7 +4825,7 @@
         <v>5</v>
       </c>
       <c r="AI34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ34">
         <v>5</v>
@@ -4798,10 +4837,10 @@
         <v>8</v>
       </c>
       <c r="AM34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO34">
         <v>-1</v>
@@ -5033,10 +5072,10 @@
         <v>100</v>
       </c>
       <c r="W4">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="X4">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Y4">
         <v>100</v>
@@ -5146,7 +5185,7 @@
         <v>100</v>
       </c>
       <c r="AC5">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="AD5">
         <v>100</v>
@@ -5223,7 +5262,7 @@
         <v>100</v>
       </c>
       <c r="W6">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="X6">
         <v>100</v>
@@ -5232,16 +5271,16 @@
         <v>100</v>
       </c>
       <c r="Z6">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="AA6">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="AB6">
         <v>100</v>
       </c>
       <c r="AC6">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="AD6">
         <v>100</v>
@@ -5318,28 +5357,28 @@
         <v>100</v>
       </c>
       <c r="W7">
-        <v>90.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="X7">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Y7">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Z7">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="AA7">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="AB7">
         <v>100</v>
       </c>
       <c r="AC7">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="AD7">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AE7">
         <v>100</v>
@@ -5413,28 +5452,28 @@
         <v>100</v>
       </c>
       <c r="W8">
-        <v>90.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="X8">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Y8">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Z8">
         <v>100</v>
       </c>
       <c r="AA8">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="AB8">
         <v>100</v>
       </c>
       <c r="AC8">
-        <v>100</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AD8">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AE8">
         <v>100</v>
@@ -5505,22 +5544,22 @@
         <v>100</v>
       </c>
       <c r="V9">
-        <v>87.09999999999999</v>
+        <v>90.2</v>
       </c>
       <c r="W9">
-        <v>81.8</v>
+        <v>81.3</v>
       </c>
       <c r="X9">
         <v>100</v>
       </c>
       <c r="Y9">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="Z9">
-        <v>94</v>
+        <v>93.8</v>
       </c>
       <c r="AA9">
-        <v>90</v>
+        <v>91.3</v>
       </c>
       <c r="AB9">
         <v>100</v>
@@ -5529,7 +5568,7 @@
         <v>93.8</v>
       </c>
       <c r="AD9">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="AE9">
         <v>100</v>
@@ -5603,10 +5642,10 @@
         <v>100</v>
       </c>
       <c r="W10">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X10">
-        <v>90.90000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="Y10">
         <v>100</v>
@@ -5621,7 +5660,7 @@
         <v>100</v>
       </c>
       <c r="AC10">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AD10">
         <v>100</v>
@@ -5695,28 +5734,28 @@
         <v>100</v>
       </c>
       <c r="V11">
-        <v>94.3</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="W11">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="X11">
         <v>100</v>
       </c>
       <c r="Y11">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Z11">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="AA11">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="AB11">
         <v>100</v>
       </c>
       <c r="AC11">
-        <v>96.90000000000001</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AD11">
         <v>100</v>
@@ -5790,31 +5829,31 @@
         <v>100</v>
       </c>
       <c r="V12">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="W12">
-        <v>86.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="X12">
         <v>100</v>
       </c>
       <c r="Y12">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Z12">
-        <v>98</v>
+        <v>96.3</v>
       </c>
       <c r="AA12">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="AB12">
         <v>100</v>
       </c>
       <c r="AC12">
-        <v>87.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="AD12">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="AE12">
         <v>100</v>
@@ -5888,7 +5927,7 @@
         <v>100</v>
       </c>
       <c r="W13">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="X13">
         <v>100</v>
@@ -5980,19 +6019,19 @@
         <v>100</v>
       </c>
       <c r="V14">
-        <v>95.7</v>
+        <v>93.8</v>
       </c>
       <c r="W14">
-        <v>86.40000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="X14">
-        <v>95.5</v>
+        <v>96.8</v>
       </c>
       <c r="Y14">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Z14">
-        <v>96</v>
+        <v>97.5</v>
       </c>
       <c r="AA14">
         <v>100</v>
@@ -6001,10 +6040,10 @@
         <v>100</v>
       </c>
       <c r="AC14">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="AD14">
-        <v>90</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="AE14">
         <v>100</v>
@@ -6075,22 +6114,22 @@
         <v>100</v>
       </c>
       <c r="V15">
-        <v>94.3</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="W15">
-        <v>81.8</v>
+        <v>81.3</v>
       </c>
       <c r="X15">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Y15">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Z15">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="AA15">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="AB15">
         <v>100</v>
@@ -6099,7 +6138,7 @@
         <v>93.8</v>
       </c>
       <c r="AD15">
-        <v>95</v>
+        <v>92.2</v>
       </c>
       <c r="AE15">
         <v>100</v>
@@ -6170,16 +6209,16 @@
         <v>100</v>
       </c>
       <c r="V16">
-        <v>100</v>
+        <v>98.2</v>
       </c>
       <c r="W16">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="X16">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Y16">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Z16">
         <v>100</v>
@@ -6191,7 +6230,7 @@
         <v>100</v>
       </c>
       <c r="AC16">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="AD16">
         <v>100</v>
@@ -6265,31 +6304,31 @@
         <v>100</v>
       </c>
       <c r="V17">
-        <v>97.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="W17">
-        <v>77.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="X17">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Y17">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="Z17">
         <v>95</v>
       </c>
-      <c r="Z17">
-        <v>96</v>
-      </c>
       <c r="AA17">
-        <v>94</v>
+        <v>96.3</v>
       </c>
       <c r="AB17">
         <v>100</v>
       </c>
       <c r="AC17">
+        <v>97.90000000000001</v>
+      </c>
+      <c r="AD17">
         <v>96.90000000000001</v>
-      </c>
-      <c r="AD17">
-        <v>95</v>
       </c>
       <c r="AE17">
         <v>100</v>
@@ -6363,10 +6402,10 @@
         <v>100</v>
       </c>
       <c r="W18">
-        <v>90.90000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="X18">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Y18">
         <v>100</v>
@@ -6375,13 +6414,13 @@
         <v>100</v>
       </c>
       <c r="AA18">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="AB18">
         <v>100</v>
       </c>
       <c r="AC18">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="AD18">
         <v>100</v>
@@ -6455,31 +6494,31 @@
         <v>100</v>
       </c>
       <c r="V19">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="W19">
-        <v>81.8</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="X19">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Y19">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Z19">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="AA19">
-        <v>96</v>
+        <v>96.3</v>
       </c>
       <c r="AB19">
         <v>100</v>
       </c>
       <c r="AC19">
+        <v>95.8</v>
+      </c>
+      <c r="AD19">
         <v>93.8</v>
-      </c>
-      <c r="AD19">
-        <v>90</v>
       </c>
       <c r="AE19">
         <v>100</v>
@@ -6553,7 +6592,7 @@
         <v>100</v>
       </c>
       <c r="W20">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="X20">
         <v>100</v>
@@ -6571,7 +6610,7 @@
         <v>100</v>
       </c>
       <c r="AC20">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="AD20">
         <v>100</v>
@@ -6648,19 +6687,19 @@
         <v>100</v>
       </c>
       <c r="W21">
-        <v>86.40000000000001</v>
+        <v>87.5</v>
       </c>
       <c r="X21">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Y21">
         <v>100</v>
       </c>
       <c r="Z21">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="AA21">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="AB21">
         <v>100</v>
@@ -6743,28 +6782,28 @@
         <v>100</v>
       </c>
       <c r="W22">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="X22">
-        <v>90.90000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="Y22">
+        <v>96.90000000000001</v>
+      </c>
+      <c r="Z22">
+        <v>96.3</v>
+      </c>
+      <c r="AA22">
         <v>95</v>
       </c>
-      <c r="Z22">
-        <v>98</v>
-      </c>
-      <c r="AA22">
-        <v>96</v>
-      </c>
       <c r="AB22">
         <v>100</v>
       </c>
       <c r="AC22">
-        <v>90.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="AD22">
-        <v>97.5</v>
+        <v>93.8</v>
       </c>
       <c r="AE22">
         <v>100</v>
@@ -6835,28 +6874,28 @@
         <v>100</v>
       </c>
       <c r="V23">
-        <v>98.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="W23">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="X23">
-        <v>95.5</v>
+        <v>96.8</v>
       </c>
       <c r="Y23">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Z23">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AA23">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="AB23">
         <v>100</v>
       </c>
       <c r="AC23">
-        <v>93.8</v>
+        <v>95.8</v>
       </c>
       <c r="AD23">
         <v>100</v>
@@ -6930,28 +6969,28 @@
         <v>100</v>
       </c>
       <c r="V24">
-        <v>94.3</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="W24">
-        <v>90.90000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="X24">
-        <v>90.90000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="Y24">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Z24">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="AA24">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="AB24">
         <v>100</v>
       </c>
       <c r="AC24">
-        <v>81.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="AD24">
         <v>100</v>
@@ -7025,31 +7064,31 @@
         <v>100</v>
       </c>
       <c r="V25">
-        <v>92.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="W25">
-        <v>68.2</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="X25">
-        <v>86.40000000000001</v>
+        <v>76.2</v>
       </c>
       <c r="Y25">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Z25">
-        <v>84</v>
+        <v>86.3</v>
       </c>
       <c r="AA25">
-        <v>90</v>
+        <v>91.3</v>
       </c>
       <c r="AB25">
         <v>100</v>
       </c>
       <c r="AC25">
-        <v>71.90000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="AD25">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="AE25">
         <v>100</v>
@@ -7123,10 +7162,10 @@
         <v>100</v>
       </c>
       <c r="W26">
-        <v>90.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="X26">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Y26">
         <v>100</v>
@@ -7141,7 +7180,7 @@
         <v>100</v>
       </c>
       <c r="AC26">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="AD26">
         <v>100</v>
@@ -7218,7 +7257,7 @@
         <v>100</v>
       </c>
       <c r="W27">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X27">
         <v>100</v>
@@ -7227,10 +7266,10 @@
         <v>100</v>
       </c>
       <c r="Z27">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="AA27">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="AB27">
         <v>100</v>
@@ -7310,10 +7349,10 @@
         <v>100</v>
       </c>
       <c r="V28">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="W28">
-        <v>90.90000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="X28">
         <v>100</v>
@@ -7322,19 +7361,19 @@
         <v>100</v>
       </c>
       <c r="Z28">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="AA28">
-        <v>100</v>
+        <v>98.8</v>
       </c>
       <c r="AB28">
         <v>100</v>
       </c>
       <c r="AC28">
-        <v>87.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="AD28">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AE28">
         <v>100</v>
@@ -7408,10 +7447,10 @@
         <v>100</v>
       </c>
       <c r="W29">
-        <v>95.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="X29">
-        <v>97.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="Y29">
         <v>100</v>
@@ -7426,7 +7465,7 @@
         <v>100</v>
       </c>
       <c r="AC29">
-        <v>96.90000000000001</v>
+        <v>95.8</v>
       </c>
       <c r="AD29">
         <v>100</v>
@@ -7503,7 +7542,7 @@
         <v>100</v>
       </c>
       <c r="W30">
-        <v>95.5</v>
+        <v>93.8</v>
       </c>
       <c r="X30">
         <v>100</v>
@@ -7595,31 +7634,31 @@
         <v>100</v>
       </c>
       <c r="V31">
-        <v>98.59999999999999</v>
+        <v>97.3</v>
       </c>
       <c r="W31">
-        <v>72.7</v>
+        <v>75</v>
       </c>
       <c r="X31">
-        <v>88.59999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="Y31">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="Z31">
-        <v>98</v>
+        <v>98.8</v>
       </c>
       <c r="AA31">
-        <v>98</v>
+        <v>97.5</v>
       </c>
       <c r="AB31">
         <v>100</v>
       </c>
       <c r="AC31">
-        <v>90.59999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="AD31">
-        <v>87.5</v>
+        <v>92.2</v>
       </c>
       <c r="AE31">
         <v>100</v>
@@ -7690,13 +7729,13 @@
         <v>100</v>
       </c>
       <c r="V32">
-        <v>97.09999999999999</v>
+        <v>98.2</v>
       </c>
       <c r="W32">
-        <v>86.40000000000001</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="X32">
-        <v>90.90000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="Y32">
         <v>100</v>
@@ -7711,10 +7750,10 @@
         <v>100</v>
       </c>
       <c r="AC32">
-        <v>87.5</v>
+        <v>91.7</v>
       </c>
       <c r="AD32">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
       <c r="AE32">
         <v>100</v>
@@ -7785,31 +7824,31 @@
         <v>100</v>
       </c>
       <c r="V33">
-        <v>98.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="W33">
-        <v>63.6</v>
+        <v>62.5</v>
       </c>
       <c r="X33">
-        <v>90.90000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="Y33">
-        <v>75</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="Z33">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="AA33">
-        <v>94</v>
+        <v>96.3</v>
       </c>
       <c r="AB33">
         <v>100</v>
       </c>
       <c r="AC33">
-        <v>81.3</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="AD33">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="AE33">
         <v>100</v>
@@ -7880,22 +7919,22 @@
         <v>100</v>
       </c>
       <c r="V34">
-        <v>95.7</v>
+        <v>93.8</v>
       </c>
       <c r="W34">
-        <v>77.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="X34">
-        <v>90.90000000000001</v>
+        <v>93.7</v>
       </c>
       <c r="Y34">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="Z34">
-        <v>96</v>
+        <v>92.5</v>
       </c>
       <c r="AA34">
-        <v>96</v>
+        <v>92.5</v>
       </c>
       <c r="AB34">
         <v>100</v>
@@ -7904,7 +7943,7 @@
         <v>93.8</v>
       </c>
       <c r="AD34">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AE34">
         <v>100</v>
@@ -8002,19 +8041,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F3" s="2">
-        <v>64.5</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="G3" s="2">
-        <v>35.5</v>
+        <v>22.6</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -8025,7 +8064,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
@@ -8034,19 +8073,19 @@
         <v>31</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F4" s="2">
-        <v>77.40000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="G4" s="2">
-        <v>22.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -8057,7 +8096,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
@@ -8066,19 +8105,19 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2">
-        <v>77.40000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="G5" s="2">
-        <v>22.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -8098,19 +8137,19 @@
         <v>31</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F6" s="2">
-        <v>80.59999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="G6" s="2">
-        <v>19.4</v>
+        <v>6.5</v>
       </c>
       <c r="H6">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -8121,7 +8160,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>64</v>
@@ -8130,19 +8169,19 @@
         <v>31</v>
       </c>
       <c r="D7">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F7" s="2">
-        <v>83.90000000000001</v>
+        <v>93.5</v>
       </c>
       <c r="G7" s="2">
-        <v>16.1</v>
+        <v>6.5</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -8153,28 +8192,28 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C8">
         <v>31</v>
       </c>
       <c r="D8">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E8">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2">
-        <v>83.90000000000001</v>
+        <v>96.8</v>
       </c>
       <c r="G8" s="2">
-        <v>16.1</v>
+        <v>3.2</v>
       </c>
       <c r="H8">
-        <v>8.1</v>
+        <v>7.2</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -8185,28 +8224,28 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C9">
         <v>31</v>
       </c>
       <c r="D9">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="E9">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F9" s="2">
-        <v>83.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="G9" s="2">
-        <v>16.1</v>
+        <v>0</v>
       </c>
       <c r="H9">
-        <v>7</v>
+        <v>7.3</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -8217,28 +8256,28 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C10">
         <v>31</v>
       </c>
       <c r="D10">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E10">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F10" s="2">
-        <v>87.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="G10" s="2">
-        <v>12.9</v>
+        <v>0</v>
       </c>
       <c r="H10">
-        <v>7.1</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -8249,7 +8288,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
         <v>67</v>
@@ -8270,7 +8309,7 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -8320,7 +8359,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8352,16 +8391,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920160</v>
+        <v>23330051920342</v>
       </c>
       <c r="B2" t="s">
         <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -8375,16 +8414,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920160</v>
+        <v>23330051920342</v>
       </c>
       <c r="B3" t="s">
         <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="E3" t="s">
         <v>14</v>
@@ -8398,16 +8437,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920161</v>
+        <v>23330051920164</v>
       </c>
       <c r="B4" t="s">
         <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -8421,16 +8460,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>23330051920161</v>
+        <v>23330051920164</v>
       </c>
       <c r="B5" t="s">
         <v>73</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="E5" t="s">
         <v>14</v>
@@ -8444,22 +8483,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>23330051920166</v>
+        <v>23330051920313</v>
       </c>
       <c r="B6" t="s">
         <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -8467,16 +8506,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>23330051920166</v>
+        <v>23330051920313</v>
       </c>
       <c r="B7" t="s">
         <v>74</v>
       </c>
       <c r="C7" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="E7" t="s">
         <v>14</v>
@@ -8490,16 +8529,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>23330051920152</v>
+        <v>23330051920151</v>
       </c>
       <c r="B8" t="s">
         <v>75</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="E8" t="s">
         <v>14</v>
@@ -8513,16 +8552,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>23330051920153</v>
+        <v>23330051920152</v>
       </c>
       <c r="B9" t="s">
         <v>76</v>
       </c>
       <c r="C9" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
         <v>14</v>
@@ -8536,16 +8575,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>23330051920155</v>
+        <v>23330051920153</v>
       </c>
       <c r="B10" t="s">
         <v>77</v>
       </c>
       <c r="C10" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="E10" t="s">
         <v>14</v>
@@ -8559,16 +8598,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>23330051920154</v>
+        <v>23330051920155</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C11" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="E11" t="s">
         <v>14</v>
@@ -8582,16 +8621,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>23330051920250</v>
+        <v>23330051920154</v>
       </c>
       <c r="B12" t="s">
         <v>78</v>
       </c>
       <c r="C12" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="E12" t="s">
         <v>14</v>
@@ -8605,16 +8644,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>23330051920157</v>
+        <v>23330051920325</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C13" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="E13" t="s">
         <v>14</v>
@@ -8628,16 +8667,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>23330051920158</v>
+        <v>23330051920250</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="D14" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="E14" t="s">
         <v>14</v>
@@ -8651,16 +8690,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>23330051920159</v>
+        <v>23330051920157</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="D15" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="E15" t="s">
         <v>14</v>
@@ -8674,16 +8713,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>23330051920163</v>
+        <v>23330051920158</v>
       </c>
       <c r="B16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="D16" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="E16" t="s">
         <v>14</v>
@@ -8697,16 +8736,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>23330051920297</v>
+        <v>23330051920159</v>
       </c>
       <c r="B17" t="s">
         <v>80</v>
       </c>
       <c r="C17" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D17" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="E17" t="s">
         <v>14</v>
@@ -8720,16 +8759,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>23330051920167</v>
+        <v>23330051920160</v>
       </c>
       <c r="B18" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C18" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="D18" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="E18" t="s">
         <v>14</v>
@@ -8743,16 +8782,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>23330051920310</v>
+        <v>23330051920161</v>
       </c>
       <c r="B19" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="D19" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="E19" t="s">
         <v>14</v>
@@ -8766,16 +8805,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>23330051920169</v>
+        <v>23330051920163</v>
       </c>
       <c r="B20" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C20" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="D20" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E20" t="s">
         <v>14</v>
@@ -8789,16 +8828,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>23330051920354</v>
+        <v>23330051920297</v>
       </c>
       <c r="B21" t="s">
         <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>98</v>
+        <v>72</v>
       </c>
       <c r="D21" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E21" t="s">
         <v>14</v>
@@ -8812,16 +8851,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>23330051920170</v>
+        <v>23330051920165</v>
       </c>
       <c r="B22" t="s">
         <v>84</v>
       </c>
       <c r="C22" t="s">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="D22" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="E22" t="s">
         <v>14</v>
@@ -8835,16 +8874,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>23330051920173</v>
+        <v>23330051920166</v>
       </c>
       <c r="B23" t="s">
         <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="D23" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="E23" t="s">
         <v>14</v>
@@ -8858,16 +8897,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>23330051920172</v>
+        <v>23330051920167</v>
       </c>
       <c r="B24" t="s">
         <v>86</v>
       </c>
       <c r="C24" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="D24" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="E24" t="s">
         <v>14</v>
@@ -8881,16 +8920,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>23330051920174</v>
+        <v>23330051920310</v>
       </c>
       <c r="B25" t="s">
         <v>87</v>
       </c>
       <c r="C25" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="D25" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E25" t="s">
         <v>14</v>
@@ -8899,6 +8938,144 @@
         <v>59</v>
       </c>
       <c r="G25">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>23330051920169</v>
+      </c>
+      <c r="B26" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" t="s">
+        <v>104</v>
+      </c>
+      <c r="D26" t="s">
+        <v>129</v>
+      </c>
+      <c r="E26" t="s">
+        <v>14</v>
+      </c>
+      <c r="F26" t="s">
+        <v>59</v>
+      </c>
+      <c r="G26">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>23330051920354</v>
+      </c>
+      <c r="B27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" t="s">
+        <v>105</v>
+      </c>
+      <c r="D27" t="s">
+        <v>130</v>
+      </c>
+      <c r="E27" t="s">
+        <v>14</v>
+      </c>
+      <c r="F27" t="s">
+        <v>59</v>
+      </c>
+      <c r="G27">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>23330051920170</v>
+      </c>
+      <c r="B28" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" t="s">
+        <v>106</v>
+      </c>
+      <c r="D28" t="s">
+        <v>131</v>
+      </c>
+      <c r="E28" t="s">
+        <v>14</v>
+      </c>
+      <c r="F28" t="s">
+        <v>59</v>
+      </c>
+      <c r="G28">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>23330051920173</v>
+      </c>
+      <c r="B29" t="s">
+        <v>90</v>
+      </c>
+      <c r="C29" t="s">
+        <v>107</v>
+      </c>
+      <c r="D29" t="s">
+        <v>132</v>
+      </c>
+      <c r="E29" t="s">
+        <v>14</v>
+      </c>
+      <c r="F29" t="s">
+        <v>59</v>
+      </c>
+      <c r="G29">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>23330051920172</v>
+      </c>
+      <c r="B30" t="s">
+        <v>91</v>
+      </c>
+      <c r="C30" t="s">
+        <v>72</v>
+      </c>
+      <c r="D30" t="s">
+        <v>133</v>
+      </c>
+      <c r="E30" t="s">
+        <v>14</v>
+      </c>
+      <c r="F30" t="s">
+        <v>59</v>
+      </c>
+      <c r="G30">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>23330051920174</v>
+      </c>
+      <c r="B31" t="s">
+        <v>92</v>
+      </c>
+      <c r="C31" t="s">
+        <v>92</v>
+      </c>
+      <c r="D31" t="s">
+        <v>134</v>
+      </c>
+      <c r="E31" t="s">
+        <v>14</v>
+      </c>
+      <c r="F31" t="s">
+        <v>59</v>
+      </c>
+      <c r="G31">
         <v>-1</v>
       </c>
     </row>

--- a/grupos/2APM - Estadisticos 20232.xlsx
+++ b/grupos/2APM - Estadisticos 20232.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="82">
   <si>
     <t>Materia</t>
   </si>
@@ -197,9 +197,6 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>Vargas Olvera Francisco Eduardo</t>
-  </si>
-  <si>
     <t>Gaspar Velazco Juan Francisco</t>
   </si>
   <si>
@@ -224,6 +221,9 @@
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
+    <t>Vargas Olvera Francisco Eduardo</t>
+  </si>
+  <si>
     <t>NC</t>
   </si>
   <si>
@@ -236,6 +236,9 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
@@ -245,103 +248,13 @@
     <t>VIVANCO</t>
   </si>
   <si>
-    <t>ABREGO</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>BONILLA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MELO</t>
-  </si>
-  <si>
-    <t>MOLINA</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
+    <t>CERON</t>
   </si>
   <si>
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>TOLENTINO</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>NIEVES</t>
-  </si>
-  <si>
-    <t>ANDRADE</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>TETLA</t>
-  </si>
-  <si>
-    <t>AMADOR</t>
-  </si>
-  <si>
-    <t>TENCHIPE</t>
-  </si>
-  <si>
-    <t>COXCAHUA</t>
-  </si>
-  <si>
-    <t>MONTIEL</t>
-  </si>
-  <si>
-    <t>CORREA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
+    <t>KEVIN IVAN</t>
   </si>
   <si>
     <t>YAMILET</t>
@@ -351,78 +264,6 @@
   </si>
   <si>
     <t>LUIS AARON</t>
-  </si>
-  <si>
-    <t>SULU ALAN</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>ESTRELLA ESMERALDA</t>
-  </si>
-  <si>
-    <t>ESTRELLA RUBI</t>
-  </si>
-  <si>
-    <t>XOCHITL ALELI</t>
-  </si>
-  <si>
-    <t>ANDREA</t>
-  </si>
-  <si>
-    <t>JAIR</t>
-  </si>
-  <si>
-    <t>DORIAN ALEXANDER</t>
-  </si>
-  <si>
-    <t>JUAN PABLO</t>
-  </si>
-  <si>
-    <t>HECTOR</t>
-  </si>
-  <si>
-    <t>JOSELYN</t>
-  </si>
-  <si>
-    <t>KEIRA</t>
-  </si>
-  <si>
-    <t>URIEL</t>
-  </si>
-  <si>
-    <t>KENYA MARIANA</t>
-  </si>
-  <si>
-    <t>LEONARDO GABRIEL</t>
-  </si>
-  <si>
-    <t>SALMA JANET</t>
-  </si>
-  <si>
-    <t>JESHUA</t>
-  </si>
-  <si>
-    <t>VICTOR JESUS</t>
-  </si>
-  <si>
-    <t>ELIUD EDUARDO</t>
-  </si>
-  <si>
-    <t>KAORY AYELEN</t>
-  </si>
-  <si>
-    <t>MARIEL</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>JUAN CARLOS</t>
   </si>
 </sst>
 </file>
@@ -1093,7 +934,7 @@
         <v>6</v>
       </c>
       <c r="AO4">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:41">
@@ -1218,7 +1059,7 @@
         <v>9</v>
       </c>
       <c r="AO5">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:41">
@@ -1343,7 +1184,7 @@
         <v>7</v>
       </c>
       <c r="AO6">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:41">
@@ -1468,7 +1309,7 @@
         <v>6</v>
       </c>
       <c r="AO7">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:41">
@@ -1593,7 +1434,7 @@
         <v>6</v>
       </c>
       <c r="AO8">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:41">
@@ -1718,7 +1559,7 @@
         <v>6</v>
       </c>
       <c r="AO9">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:41">
@@ -1843,7 +1684,7 @@
         <v>6</v>
       </c>
       <c r="AO10">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:41">
@@ -1968,7 +1809,7 @@
         <v>6</v>
       </c>
       <c r="AO11">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:41">
@@ -2093,7 +1934,7 @@
         <v>7</v>
       </c>
       <c r="AO12">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:41">
@@ -2218,7 +2059,7 @@
         <v>7</v>
       </c>
       <c r="AO13">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:41">
@@ -2343,7 +2184,7 @@
         <v>8</v>
       </c>
       <c r="AO14">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:41">
@@ -2468,7 +2309,7 @@
         <v>6</v>
       </c>
       <c r="AO15">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:41">
@@ -2593,7 +2434,7 @@
         <v>8</v>
       </c>
       <c r="AO16">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:41">
@@ -2718,7 +2559,7 @@
         <v>5</v>
       </c>
       <c r="AO17">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:41">
@@ -2843,7 +2684,7 @@
         <v>8</v>
       </c>
       <c r="AO18">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:41">
@@ -2968,7 +2809,7 @@
         <v>6</v>
       </c>
       <c r="AO19">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:41">
@@ -3093,7 +2934,7 @@
         <v>7</v>
       </c>
       <c r="AO20">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:41">
@@ -3218,7 +3059,7 @@
         <v>6</v>
       </c>
       <c r="AO21">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:41">
@@ -3343,7 +3184,7 @@
         <v>6</v>
       </c>
       <c r="AO22">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:41">
@@ -3468,7 +3309,7 @@
         <v>7</v>
       </c>
       <c r="AO23">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:41">
@@ -3593,7 +3434,7 @@
         <v>8</v>
       </c>
       <c r="AO24">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:41">
@@ -3718,7 +3559,7 @@
         <v>5</v>
       </c>
       <c r="AO25">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:41">
@@ -3843,7 +3684,7 @@
         <v>7</v>
       </c>
       <c r="AO26">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:41">
@@ -3968,7 +3809,7 @@
         <v>9</v>
       </c>
       <c r="AO27">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:41">
@@ -4093,7 +3934,7 @@
         <v>6</v>
       </c>
       <c r="AO28">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:41">
@@ -4218,7 +4059,7 @@
         <v>9</v>
       </c>
       <c r="AO29">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:41">
@@ -4343,7 +4184,7 @@
         <v>10</v>
       </c>
       <c r="AO30">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:41">
@@ -4468,7 +4309,7 @@
         <v>5</v>
       </c>
       <c r="AO31">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:41">
@@ -4593,7 +4434,7 @@
         <v>6</v>
       </c>
       <c r="AO32">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:41">
@@ -4718,7 +4559,7 @@
         <v>6</v>
       </c>
       <c r="AO33">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="34" spans="1:41">
@@ -4843,7 +4684,7 @@
         <v>6</v>
       </c>
       <c r="AO34">
-        <v>-1</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -8003,7 +7844,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>59</v>
@@ -8012,27 +7853,30 @@
         <v>31</v>
       </c>
       <c r="D2">
+        <v>24</v>
+      </c>
+      <c r="E2">
+        <v>7</v>
+      </c>
+      <c r="F2" s="2">
+        <v>77.40000000000001</v>
+      </c>
+      <c r="G2" s="2">
+        <v>22.6</v>
+      </c>
+      <c r="H2">
+        <v>6.9</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2" s="2">
         <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>31</v>
-      </c>
-      <c r="J2" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>60</v>
@@ -8041,19 +7885,19 @@
         <v>31</v>
       </c>
       <c r="D3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="F3" s="2">
-        <v>77.40000000000001</v>
+        <v>90.3</v>
       </c>
       <c r="G3" s="2">
-        <v>22.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -8064,7 +7908,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
         <v>61</v>
@@ -8085,7 +7929,7 @@
         <v>9.699999999999999</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>6.8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -8096,7 +7940,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>62</v>
@@ -8105,19 +7949,19 @@
         <v>31</v>
       </c>
       <c r="D5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" s="2">
-        <v>90.3</v>
+        <v>93.5</v>
       </c>
       <c r="G5" s="2">
-        <v>9.699999999999999</v>
+        <v>6.5</v>
       </c>
       <c r="H5">
-        <v>6.8</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -8128,7 +7972,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>63</v>
@@ -8149,7 +7993,7 @@
         <v>6.5</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -8160,28 +8004,28 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C7">
         <v>31</v>
       </c>
       <c r="D7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F7" s="2">
-        <v>93.5</v>
+        <v>96.8</v>
       </c>
       <c r="G7" s="2">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="H7">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -8192,7 +8036,7 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>64</v>
@@ -8201,19 +8045,19 @@
         <v>31</v>
       </c>
       <c r="D8">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" s="2">
-        <v>96.8</v>
+        <v>100</v>
       </c>
       <c r="G8" s="2">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="H8">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -8224,7 +8068,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
         <v>65</v>
@@ -8245,7 +8089,7 @@
         <v>0</v>
       </c>
       <c r="H9">
-        <v>7.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -8256,7 +8100,7 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>66</v>
@@ -8277,7 +8121,7 @@
         <v>0</v>
       </c>
       <c r="H10">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -8288,7 +8132,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B11" t="s">
         <v>67</v>
@@ -8309,7 +8153,7 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>8.4</v>
+        <v>10</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -8359,7 +8203,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8391,22 +8235,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>23330051920342</v>
+        <v>23330051920162</v>
       </c>
       <c r="B2" t="s">
         <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D2" t="s">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -8414,45 +8258,45 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>23330051920342</v>
+        <v>23330051920162</v>
       </c>
       <c r="B3" t="s">
         <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D3" t="s">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>23330051920164</v>
+        <v>23330051920342</v>
       </c>
       <c r="B4" t="s">
         <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="D4" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -8463,22 +8307,22 @@
         <v>23330051920164</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="D5" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
         <v>59</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -8486,597 +8330,22 @@
         <v>23330051920313</v>
       </c>
       <c r="B6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>110</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G6">
         <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>23330051920313</v>
-      </c>
-      <c r="B7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" t="s">
-        <v>110</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" t="s">
-        <v>59</v>
-      </c>
-      <c r="G7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>23330051920151</v>
-      </c>
-      <c r="B8" t="s">
-        <v>75</v>
-      </c>
-      <c r="C8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D8" t="s">
-        <v>111</v>
-      </c>
-      <c r="E8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" t="s">
-        <v>59</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>23330051920152</v>
-      </c>
-      <c r="B9" t="s">
-        <v>76</v>
-      </c>
-      <c r="C9" t="s">
-        <v>95</v>
-      </c>
-      <c r="D9" t="s">
-        <v>112</v>
-      </c>
-      <c r="E9" t="s">
-        <v>14</v>
-      </c>
-      <c r="F9" t="s">
-        <v>59</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>23330051920153</v>
-      </c>
-      <c r="B10" t="s">
-        <v>77</v>
-      </c>
-      <c r="C10" t="s">
-        <v>96</v>
-      </c>
-      <c r="D10" t="s">
-        <v>113</v>
-      </c>
-      <c r="E10" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" t="s">
-        <v>59</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>23330051920155</v>
-      </c>
-      <c r="B11" t="s">
-        <v>78</v>
-      </c>
-      <c r="C11" t="s">
-        <v>97</v>
-      </c>
-      <c r="D11" t="s">
-        <v>114</v>
-      </c>
-      <c r="E11" t="s">
-        <v>14</v>
-      </c>
-      <c r="F11" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>23330051920154</v>
-      </c>
-      <c r="B12" t="s">
-        <v>78</v>
-      </c>
-      <c r="C12" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" t="s">
-        <v>115</v>
-      </c>
-      <c r="E12" t="s">
-        <v>14</v>
-      </c>
-      <c r="F12" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>23330051920325</v>
-      </c>
-      <c r="B13" t="s">
-        <v>79</v>
-      </c>
-      <c r="C13" t="s">
-        <v>98</v>
-      </c>
-      <c r="D13" t="s">
-        <v>116</v>
-      </c>
-      <c r="E13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F13" t="s">
-        <v>59</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>23330051920250</v>
-      </c>
-      <c r="B14" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" t="s">
-        <v>99</v>
-      </c>
-      <c r="D14" t="s">
-        <v>117</v>
-      </c>
-      <c r="E14" t="s">
-        <v>14</v>
-      </c>
-      <c r="F14" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>23330051920157</v>
-      </c>
-      <c r="B15" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" t="s">
-        <v>100</v>
-      </c>
-      <c r="D15" t="s">
-        <v>118</v>
-      </c>
-      <c r="E15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F15" t="s">
-        <v>59</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>23330051920158</v>
-      </c>
-      <c r="B16" t="s">
-        <v>80</v>
-      </c>
-      <c r="C16" t="s">
-        <v>90</v>
-      </c>
-      <c r="D16" t="s">
-        <v>119</v>
-      </c>
-      <c r="E16" t="s">
-        <v>14</v>
-      </c>
-      <c r="F16" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>23330051920159</v>
-      </c>
-      <c r="B17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C17" t="s">
-        <v>90</v>
-      </c>
-      <c r="D17" t="s">
-        <v>120</v>
-      </c>
-      <c r="E17" t="s">
-        <v>14</v>
-      </c>
-      <c r="F17" t="s">
-        <v>59</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>23330051920160</v>
-      </c>
-      <c r="B18" t="s">
-        <v>80</v>
-      </c>
-      <c r="C18" t="s">
-        <v>101</v>
-      </c>
-      <c r="D18" t="s">
-        <v>121</v>
-      </c>
-      <c r="E18" t="s">
-        <v>14</v>
-      </c>
-      <c r="F18" t="s">
-        <v>59</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>23330051920161</v>
-      </c>
-      <c r="B19" t="s">
-        <v>81</v>
-      </c>
-      <c r="C19" t="s">
-        <v>102</v>
-      </c>
-      <c r="D19" t="s">
-        <v>122</v>
-      </c>
-      <c r="E19" t="s">
-        <v>14</v>
-      </c>
-      <c r="F19" t="s">
-        <v>59</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>23330051920163</v>
-      </c>
-      <c r="B20" t="s">
-        <v>82</v>
-      </c>
-      <c r="C20" t="s">
-        <v>103</v>
-      </c>
-      <c r="D20" t="s">
-        <v>123</v>
-      </c>
-      <c r="E20" t="s">
-        <v>14</v>
-      </c>
-      <c r="F20" t="s">
-        <v>59</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>23330051920297</v>
-      </c>
-      <c r="B21" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" t="s">
-        <v>72</v>
-      </c>
-      <c r="D21" t="s">
-        <v>124</v>
-      </c>
-      <c r="E21" t="s">
-        <v>14</v>
-      </c>
-      <c r="F21" t="s">
-        <v>59</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>23330051920165</v>
-      </c>
-      <c r="B22" t="s">
-        <v>84</v>
-      </c>
-      <c r="C22" t="s">
-        <v>79</v>
-      </c>
-      <c r="D22" t="s">
-        <v>125</v>
-      </c>
-      <c r="E22" t="s">
-        <v>14</v>
-      </c>
-      <c r="F22" t="s">
-        <v>59</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>23330051920166</v>
-      </c>
-      <c r="B23" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" t="s">
-        <v>90</v>
-      </c>
-      <c r="D23" t="s">
-        <v>126</v>
-      </c>
-      <c r="E23" t="s">
-        <v>14</v>
-      </c>
-      <c r="F23" t="s">
-        <v>59</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>23330051920167</v>
-      </c>
-      <c r="B24" t="s">
-        <v>86</v>
-      </c>
-      <c r="C24" t="s">
-        <v>100</v>
-      </c>
-      <c r="D24" t="s">
-        <v>127</v>
-      </c>
-      <c r="E24" t="s">
-        <v>14</v>
-      </c>
-      <c r="F24" t="s">
-        <v>59</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>23330051920310</v>
-      </c>
-      <c r="B25" t="s">
-        <v>87</v>
-      </c>
-      <c r="C25" t="s">
-        <v>81</v>
-      </c>
-      <c r="D25" t="s">
-        <v>128</v>
-      </c>
-      <c r="E25" t="s">
-        <v>14</v>
-      </c>
-      <c r="F25" t="s">
-        <v>59</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>23330051920169</v>
-      </c>
-      <c r="B26" t="s">
-        <v>88</v>
-      </c>
-      <c r="C26" t="s">
-        <v>104</v>
-      </c>
-      <c r="D26" t="s">
-        <v>129</v>
-      </c>
-      <c r="E26" t="s">
-        <v>14</v>
-      </c>
-      <c r="F26" t="s">
-        <v>59</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>23330051920354</v>
-      </c>
-      <c r="B27" t="s">
-        <v>88</v>
-      </c>
-      <c r="C27" t="s">
-        <v>105</v>
-      </c>
-      <c r="D27" t="s">
-        <v>130</v>
-      </c>
-      <c r="E27" t="s">
-        <v>14</v>
-      </c>
-      <c r="F27" t="s">
-        <v>59</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>23330051920170</v>
-      </c>
-      <c r="B28" t="s">
-        <v>89</v>
-      </c>
-      <c r="C28" t="s">
-        <v>106</v>
-      </c>
-      <c r="D28" t="s">
-        <v>131</v>
-      </c>
-      <c r="E28" t="s">
-        <v>14</v>
-      </c>
-      <c r="F28" t="s">
-        <v>59</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>23330051920173</v>
-      </c>
-      <c r="B29" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" t="s">
-        <v>107</v>
-      </c>
-      <c r="D29" t="s">
-        <v>132</v>
-      </c>
-      <c r="E29" t="s">
-        <v>14</v>
-      </c>
-      <c r="F29" t="s">
-        <v>59</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>23330051920172</v>
-      </c>
-      <c r="B30" t="s">
-        <v>91</v>
-      </c>
-      <c r="C30" t="s">
-        <v>72</v>
-      </c>
-      <c r="D30" t="s">
-        <v>133</v>
-      </c>
-      <c r="E30" t="s">
-        <v>14</v>
-      </c>
-      <c r="F30" t="s">
-        <v>59</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>23330051920174</v>
-      </c>
-      <c r="B31" t="s">
-        <v>92</v>
-      </c>
-      <c r="C31" t="s">
-        <v>92</v>
-      </c>
-      <c r="D31" t="s">
-        <v>134</v>
-      </c>
-      <c r="E31" t="s">
-        <v>14</v>
-      </c>
-      <c r="F31" t="s">
-        <v>59</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>
